--- a/jogos_2025-03-10.xlsx
+++ b/jogos_2025-03-10.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="N4" t="n">
-        <v>2.78</v>
+        <v>3.09</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="S4" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="X4" t="n">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AC4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['30']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45726.41666666666</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="M6" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.09</v>
+        <v>2.78</v>
       </c>
       <c r="O6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X6" t="n">
         <v>2.95</v>
       </c>
-      <c r="P6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="Y6" t="n">
         <v>2.15</v>
       </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Z6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AI6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['45']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2.45</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45726.41666666666</v>
@@ -1536,35 +1536,35 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.08</v>
+        <v>2.63</v>
       </c>
       <c r="M9" t="n">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="N9" t="n">
-        <v>3.66</v>
+        <v>2.63</v>
       </c>
       <c r="O9" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
         <v>1.07</v>
       </c>
       <c r="W9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['45+3']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.4</v>
       </c>
-      <c r="X9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45726.5</v>
@@ -1665,35 +1665,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.63</v>
+        <v>2.08</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="N10" t="n">
-        <v>2.63</v>
+        <v>3.66</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
         <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['45+3']</t>
-        </is>
-      </c>
       <c r="AG10" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45726.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hebar 1918</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
+      <c r="T11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1.83</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="AD11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI11" t="n">
         <v>1.44</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['30', '36', '45+1', '47', '57', '60']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45726.52083333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hebar 1918</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="T12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['30', '36', '45+1', '47', '57', '60']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>2.75</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['35']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>3</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45726.52083333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,19 +2062,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="M13" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>5.94</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['50', '79', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.57</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45726.58333333334</v>
@@ -2181,119 +2181,119 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="AD14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['34', '79']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['67', '83', '90+3']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>2.4</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['52', '63']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['50', '81']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>3.6</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45726.58333333334</v>
@@ -2310,119 +2310,119 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
       <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.95</v>
       </c>
-      <c r="N15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AB15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['32', '43']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI15" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AJ15" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['9', '20']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['16']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45726.58333333334</v>
@@ -2439,35 +2439,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,55 +2475,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
         <v>4.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
         <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X16" t="n">
         <v>2.88</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC16" t="n">
         <v>2</v>
@@ -2533,25 +2533,25 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['50', '79', '90+4']</t>
+          <t>['9', '20']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45726.58333333334</v>
@@ -2568,26 +2568,26 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="M17" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.22</v>
+        <v>5.75</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['52', '63']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['50', '81']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>3.6</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['32', '43']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45726.58333333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>5.94</v>
       </c>
       <c r="O18" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>6.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="T18" t="n">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="X18" t="n">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.1</v>
+        <v>2.76</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['34', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['67', '83', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.4</v>
+        <v>3.34</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45726.58333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ankaragücü</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="N19" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="P19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD19" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['61', '87']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45726.60416666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,109 +2965,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Ankaragücü</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M20" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="AD20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.17</v>
       </c>
-      <c r="X20" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['61', '87']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH20" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45726.60416666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,109 +3094,109 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O21" t="n">
         <v>4</v>
       </c>
-      <c r="H21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.5</v>
-      </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="X21" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.77</v>
+        <v>2.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.98</v>
+        <v>1.48</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AC21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD21" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['48', '59', '69', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['54', '74']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45726.625</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,19 +3223,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M22" t="n">
         <v>3.1</v>
       </c>
-      <c r="M22" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N22" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
         <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z22" t="n">
         <v>1.57</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="AA22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['45+1', '87']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI22" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y22" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['6']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45726.625</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
         <v>3</v>
       </c>
-      <c r="H23" t="n">
-        <v>3</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T23" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="AD23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['48', '59', '69', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['54', '74']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AH23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI23" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['-1', '-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['-1', '-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45726.625</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>2</v>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>3.54</v>
       </c>
       <c r="P24" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z24" t="n">
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['10', '43', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['45+1', '87']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45726.625</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X25" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z25" t="n">
         <v>2</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AA25" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['10', '43', '90+4']</t>
+          <t>['-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AG25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45726.625</v>
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,55 +4023,55 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.58</v>
+        <v>2.83</v>
       </c>
       <c r="M28" t="n">
-        <v>4.49</v>
+        <v>3.71</v>
       </c>
       <c r="N28" t="n">
-        <v>4.84</v>
+        <v>2.32</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC28" t="n">
         <v>1.57</v>
@@ -4081,25 +4081,25 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '13']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45726.66666666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.83</v>
+        <v>1.51</v>
       </c>
       <c r="M29" t="n">
-        <v>3.71</v>
+        <v>3.95</v>
       </c>
       <c r="N29" t="n">
-        <v>2.32</v>
+        <v>5.25</v>
       </c>
       <c r="O29" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="R29" t="n">
         <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.55</v>
+        <v>2.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '90', '90+4']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['3', '13']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.57</v>
+        <v>1.06</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.42</v>
+        <v>2.65</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.73</v>
+        <v>3.5</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45726.66666666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="M30" t="n">
-        <v>3.95</v>
+        <v>4.49</v>
       </c>
       <c r="N30" t="n">
-        <v>5.25</v>
+        <v>4.84</v>
       </c>
       <c r="O30" t="n">
+        <v>2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA30" t="n">
         <v>2.05</v>
       </c>
-      <c r="P30" t="n">
+      <c r="AB30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD30" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['18', '90', '90+4']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AI30" t="n">
         <v>1.36</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45726.66666666666</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,22 +4642,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4668,22 +4668,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="M33" t="n">
-        <v>3.84</v>
+        <v>3.27</v>
       </c>
       <c r="N33" t="n">
-        <v>5.3</v>
+        <v>2.91</v>
       </c>
       <c r="O33" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="R33" t="n">
         <v>1.4</v>
@@ -4692,59 +4692,59 @@
         <v>2.75</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['52', '54', '57', '80', '90']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.4</v>
       </c>
-      <c r="V33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y33" t="n">
+      <c r="AH33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI33" t="n">
         <v>1.93</v>
       </c>
-      <c r="Z33" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['32']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['22']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45726.69791666666</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,48 +4771,48 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q34" t="n">
         <v>5</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.35</v>
       </c>
       <c r="R34" t="n">
         <v>1.4</v>
@@ -4821,59 +4821,59 @@
         <v>2.75</v>
       </c>
       <c r="T34" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V34" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.33</v>
       </c>
-      <c r="X34" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC34" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['52', '54', '57', '80', '90']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45726.69791666666</v>
@@ -4890,29 +4890,29 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="O35" t="n">
         <v>3.1</v>
       </c>
-      <c r="M35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O35" t="n">
-        <v>3.75</v>
-      </c>
       <c r="P35" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="R35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W35" t="n">
         <v>1.5</v>
       </c>
-      <c r="S35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X35" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="Y35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC35" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD35" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45726.70833333334</v>
@@ -5019,29 +5019,29 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI36" t="n">
         <v>2.3</v>
       </c>
-      <c r="M36" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="O36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T36" t="n">
-        <v>4</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['90+3']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ36" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45726.70833333334</v>
@@ -5535,32 +5535,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="M40" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="N40" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="O40" t="n">
         <v>3.5</v>
       </c>
       <c r="P40" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA40" t="n">
         <v>4.33</v>
       </c>
-      <c r="R40" t="n">
+      <c r="AB40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.73</v>
       </c>
-      <c r="S40" t="n">
-        <v>2</v>
-      </c>
-      <c r="T40" t="n">
-        <v>5</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45726.79166666666</v>
@@ -5664,26 +5664,26 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>1</v>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.7</v>
+        <v>1.91</v>
       </c>
       <c r="M41" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N41" t="n">
-        <v>1.95</v>
+        <v>4.83</v>
       </c>
       <c r="O41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q41" t="n">
         <v>5</v>
       </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S41" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T41" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="U41" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="V41" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="W41" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="X41" t="n">
-        <v>3.2</v>
+        <v>2.37</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AC41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH41" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD41" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>['16']</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AI41" t="n">
-        <v>3.25</v>
+        <v>1.62</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45726.79166666666</v>
@@ -5793,119 +5793,119 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S42" t="n">
         <v>2</v>
       </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M42" t="n">
-        <v>3</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O42" t="n">
+      <c r="T42" t="n">
         <v>5</v>
       </c>
-      <c r="P42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3.75</v>
-      </c>
       <c r="U42" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="V42" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W42" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="X42" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.15</v>
+        <v>3.15</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['46']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['61', '88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.83</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AI42" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45726.79166666666</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,25 +5932,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="M43" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O43" t="n">
+        <v>5</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T43" t="n">
         <v>2.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="U43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA43" t="n">
         <v>3.5</v>
       </c>
-      <c r="P43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AB43" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AC43" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45726.79166666666</v>
@@ -6051,35 +6051,35 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G44" t="n">
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6087,22 +6087,22 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.91</v>
+        <v>3.8</v>
       </c>
       <c r="M44" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>4.83</v>
+        <v>2.05</v>
       </c>
       <c r="O44" t="n">
+        <v>5</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q44" t="n">
         <v>2.75</v>
-      </c>
-      <c r="P44" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>5</v>
       </c>
       <c r="R44" t="n">
         <v>1.57</v>
@@ -6117,53 +6117,53 @@
         <v>1.25</v>
       </c>
       <c r="V44" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X44" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AA44" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['46']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['2']</t>
+          <t>['61', '88']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.8</v>
+        <v>1.21</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="AJ44" t="n">
-        <v>3</v>
+        <v>1.66</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45726.79166666666</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Uruguay Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,45 +6190,45 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wanderers</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cerro Largo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G45" t="n">
+        <v>4</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O45" t="n">
         <v>3</v>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M45" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="N45" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="O45" t="n">
-        <v>2.9</v>
-      </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
         <v>3.5</v>
@@ -6237,44 +6237,44 @@
         <v>1.44</v>
       </c>
       <c r="S45" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T45" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U45" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V45" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W45" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="X45" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Z45" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC45" t="n">
         <v>1.73</v>
       </c>
-      <c r="AA45" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD45" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['18', '61', '78']</t>
+          <t>['3', '23', '63', '84']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -6283,16 +6283,16 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45726.83333333334</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uruguay Primera División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,45 +6319,45 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Cerro Largo</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P46" t="n">
         <v>2</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O46" t="n">
-        <v>3</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
         <v>3.5</v>
@@ -6366,44 +6366,44 @@
         <v>1.44</v>
       </c>
       <c r="S46" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T46" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U46" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V46" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W46" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="X46" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AD46" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['3', '23', '63', '84']</t>
+          <t>['18', '61', '78']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -6412,16 +6412,16 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45726.83333333334</v>
